--- a/artfynd/A 8828-2026 artfynd.xlsx
+++ b/artfynd/A 8828-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89326764</v>
+        <v>89326763</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533160.8758940779</v>
+        <v>533007</v>
       </c>
       <c r="R2" t="n">
-        <v>6323552.131469491</v>
+        <v>6323656</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-05-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>89326813</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533122.1386450345</v>
+        <v>533122</v>
       </c>
       <c r="R3" t="n">
-        <v>6323489.821594905</v>
+        <v>6323490</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2020-05-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89326762</v>
+        <v>89326815</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533022.9198351273</v>
+        <v>533137</v>
       </c>
       <c r="R4" t="n">
-        <v>6323562.993911797</v>
+        <v>6323453</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2020-05-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,16 +969,11 @@
         <v>89326816</v>
       </c>
       <c r="B5" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533153.1514658113</v>
+        <v>533153</v>
       </c>
       <c r="R5" t="n">
-        <v>6323564.034409895</v>
+        <v>6323564</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2020-05-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89326817</v>
+        <v>89326762</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,42 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Landskapet kring Hökasjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533227.0225486092</v>
+        <v>533023</v>
       </c>
       <c r="R6" t="n">
-        <v>6323593.994396346</v>
+        <v>6323563</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,19 +1131,9 @@
           <t>2020-05-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,6 +1157,208 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89326817</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Landskapet kring Hökasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>533227</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6323594</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>89326764</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Landskapet kring Hökasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533161</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6323552</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
